--- a/frontend/public/templates/products-import-template.xlsx
+++ b/frontend/public/templates/products-import-template.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="31">
   <si>
     <t>اسم الصنف</t>
   </si>
@@ -30,6 +30,12 @@
     <t>الباركود</t>
   </si>
   <si>
+    <t>الماركة</t>
+  </si>
+  <si>
+    <t>الموديل</t>
+  </si>
+  <si>
     <t>سعر التكلفة</t>
   </si>
   <si>
@@ -57,6 +63,12 @@
     <t>قطعة</t>
   </si>
   <si>
+    <t>سامسونج</t>
+  </si>
+  <si>
+    <t>A54</t>
+  </si>
+  <si>
     <t>المخزن الرئيسي</t>
   </si>
   <si>
@@ -66,22 +78,28 @@
     <t>الشرح</t>
   </si>
   <si>
-    <t>مطلوب</t>
-  </si>
-  <si>
-    <t>اختياري — اسم التصنيف الموجود في النظام</t>
-  </si>
-  <si>
-    <t>اختياري — اسم وحدة القياس الموجودة في النظام</t>
+    <t>مطلوب — اسم الصنف فقط، بدون الماركة أو الموديل</t>
+  </si>
+  <si>
+    <t>اختياري — إن لم يوجد يُنشأ تلقائياً بالاسم المكتوب</t>
+  </si>
+  <si>
+    <t>اختياري — إن فرغت تُستخدم «قطعة»؛ وإن لم توجد تُنشأ تلقائياً</t>
   </si>
   <si>
     <t>اختياري — يجب أن يكون فريداً إن وُجد</t>
   </si>
   <si>
+    <t>اختياري — عمود مستقل، لا تضعها داخل اسم الصنف</t>
+  </si>
+  <si>
+    <t>اختياري — عمود مستقل، لا تضعه داخل اسم الصنف</t>
+  </si>
+  <si>
     <t>اختياري — افتراضي 0</t>
   </si>
   <si>
-    <t>مطلوب — اسم أو رمز المخزن لربط الصنف</t>
+    <t>مطلوب — اسم أو رمز مخزن موجود. إن لم يكن لديك أي مخزن يُنشأ «المخزن الرئيسي» تلقائياً</t>
   </si>
   <si>
     <t>اختياري — تُحفظ في وصف الصنف</t>
@@ -448,22 +466,24 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12.854" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="9.283" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="16.425" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="11.711" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="16.425" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="12" max="12" width="9.283" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -494,30 +514,42 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2">
-        <v>10</v>
-      </c>
-      <c r="F2">
+      <c r="H2">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2">
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2">
         <v>0</v>
       </c>
-      <c r="I2">
+      <c r="K2">
         <v>5</v>
       </c>
     </row>
@@ -533,19 +565,19 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="52.987" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="101.404" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -553,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -561,7 +593,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -569,7 +601,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -577,7 +609,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -585,7 +617,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -593,7 +625,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -601,7 +633,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -609,7 +641,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -617,7 +649,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -625,15 +657,31 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
